--- a/11504科月會_進度說明.xlsx
+++ b/11504科月會_進度說明.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasminechang/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01948A2-091E-0349-9D42-92884B2D7E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4506"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="500" windowWidth="26860" windowHeight="17500" xr2:uid="{194EC3AD-9B26-3C4F-91C4-3A7717B318C4}"/>
+    <workbookView xWindow="1944" yWindow="504" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="昱翔" sheetId="1" r:id="rId1"/>
@@ -29,9 +23,9 @@
     <sheet name="嘉銘" sheetId="16" r:id="rId14"/>
     <sheet name="育盛" sheetId="17" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="477">
   <si>
     <t>需求單位</t>
   </si>
@@ -218,10 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>張重健</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>李嘉銘/葉靚/鄒雯芯/黃奕晴/張丞君/吳涴棋/程昱翔/盧德鴻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -300,10 +290,6 @@
 (待決議事項)：
 1. 待 IBM review</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吳涴棋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1222,6 +1208,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">60% </t>
@@ -1232,6 +1219,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1259,6 +1247,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">60% </t>
@@ -1269,6 +1258,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1299,6 +1289,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">30% </t>
@@ -1309,6 +1300,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1334,6 +1326,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">40% </t>
@@ -1344,6 +1337,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1374,6 +1368,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>5%</t>
@@ -1384,6 +1379,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1403,6 +1399,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>40%</t>
@@ -1413,6 +1410,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1450,6 +1448,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>85%</t>
@@ -1460,6 +1459,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve"> 
@@ -1481,6 +1481,7 @@
         <sz val="18"/>
         <color rgb="FFFF0000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">85% </t>
@@ -1491,6 +1492,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1519,6 +1521,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>10%</t>
@@ -1529,6 +1532,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1542,6 +1546,7 @@
         <sz val="18"/>
         <color rgb="FFFF0000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>- 等待BA確認處理方式</t>
@@ -1552,6 +1557,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1573,6 +1579,7 @@
         <sz val="18"/>
         <color rgb="FF00B050"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>10%</t>
@@ -1583,6 +1590,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1596,6 +1604,7 @@
         <sz val="18"/>
         <color rgb="FFFF0000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>- 等待BA確認處理方式</t>
@@ -1606,6 +1615,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1640,6 +1650,7 @@
         <sz val="18"/>
         <color rgb="FFFF0000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>95%</t>
@@ -1650,6 +1661,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t xml:space="preserve">
@@ -1705,6 +1717,7 @@
         <sz val="18"/>
         <color theme="0" tint="-0.499984740745262"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>100%</t>
@@ -3146,7 +3159,7 @@
 4. 2/10 開上線協調會
 (待決議事項)
 預計3/9～3/20 正式環境測試</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">(預計完成時間)：2026/03/31
@@ -3157,7 +3170,7 @@
 3. 準備驗收文件
 (待決議事項)
 </t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>信用卡中心：林廷輝經理、張重健</t>
@@ -3237,7 +3250,7 @@
   </si>
   <si>
     <t>PENDING</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>自動化測試</t>
@@ -3247,7 +3260,7 @@
     <t>(預計完成時間)：2025/09。
 (目前進度)：10%
 (報告事項)：</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>核心：徐治純</t>
@@ -3283,21 +3296,21 @@
   </si>
   <si>
     <t>ESG企業問卷報送</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>(預計完成時間)：-。
 (目前進度)：90%
 (報告事項)：程式已完成修改，後續待允杰完成憑證採購，提交測試檔案至聯徵中心進行測試作業。</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>企金部：尤雅青</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>劉令捷/ 葉靚/ 王允杰</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>需求：
@@ -3313,18 +3326,18 @@
 (目前進度)：90%
 (報告事項)：
 待金檢結束後再進行換版</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>(預計完成時間)：2026/01。
 (目前進度)：90%
 (報告事項)：
 同ESG問卷報送一同換版</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>企金部：蔡綺紋</t>
-    <phoneticPr fontId="61" type="noConversion"/>
+    <phoneticPr fontId="59" type="noConversion"/>
   </si>
   <si>
     <t>需求：
@@ -4751,6 +4764,7 @@
         <sz val="14"/>
         <color rgb="FF4EA72E"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>準時</t>
@@ -4761,6 +4775,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>)
@@ -4790,6 +4805,7 @@
         <sz val="14"/>
         <color rgb="FF4EA72E"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>準時</t>
@@ -4800,6 +4816,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>)
@@ -4811,37 +4828,6 @@
   <si>
     <t>信用卡偽冒案件處理系統CFMS</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(預計完成時間)：2026/
-(目前進度)：95% (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="9"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>準時</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>)
-(報告事項)：
-1. 資訊需求處理單 - O502 320</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>信用卡中心、資訊研發處</t>
@@ -4898,6 +4884,7 @@
         <sz val="14"/>
         <color rgb="FF4EA72E"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>準時</t>
@@ -4908,6 +4895,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>)
@@ -4930,6 +4918,7 @@
         <sz val="14"/>
         <color rgb="FF4EA72E"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>準時</t>
@@ -4940,6 +4929,7 @@
         <sz val="14"/>
         <color rgb="FF000000"/>
         <rFont val="標楷體"/>
+        <family val="4"/>
         <charset val="136"/>
       </rPr>
       <t>)
@@ -4952,23 +4942,74 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>休假</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳涴棋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>張重健</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>詳見ppt - 資訊研發處南區月報_202604_Hill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>休假</t>
+    <t>處理狀態</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(預計完成時間)：2026/
+(目前進度)：95% (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="9"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>準時</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>)
+(報告事項)：
+1. 資訊需求處理單 - O-502 320</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>O-502 320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>結案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="[$-404]General"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="[$-404]General"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="73">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5165,6 +5206,7 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5286,6 +5328,7 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5323,6 +5366,7 @@
       <sz val="18"/>
       <color rgb="FF00B050"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5330,6 +5374,7 @@
       <sz val="18"/>
       <color rgb="FFFF0000"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5352,6 +5397,7 @@
       <sz val="18"/>
       <color theme="0" tint="-0.499984740745262"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5380,24 +5426,9 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="標楷體"/>
       <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF00B050"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="標楷體"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5497,6 +5528,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
@@ -5504,6 +5536,14 @@
       <sz val="14"/>
       <color rgb="FF4EA72E"/>
       <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -5867,7 +5907,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
@@ -5882,7 +5922,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
@@ -5893,10 +5933,10 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
@@ -5912,14 +5952,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5934,13 +5974,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -5958,13 +5998,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1">
@@ -5974,13 +6014,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5989,7 +6029,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="29" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6130,13 +6170,13 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="7" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="7" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="8" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
@@ -6166,46 +6206,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="14" applyFont="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="14" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="10" xfId="14" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="10" xfId="14" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6214,46 +6254,46 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="60" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="58" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="4" applyFont="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="4" applyFont="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6277,10 +6317,10 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="65" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6292,7 +6332,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="4" applyFont="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6304,34 +6344,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="29" fillId="5" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="5" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="29" fillId="5" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="5" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="29" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6352,10 +6392,10 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="2" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6367,29 +6407,32 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
-    <cellStyle name="Excel Built-in Hyperlink" xfId="10" xr:uid="{548AC7E8-186F-F640-9A1D-7BC0BED2694B}"/>
-    <cellStyle name="Excel Built-in Normal" xfId="3" xr:uid="{A1835EC8-35A6-5748-A91A-38AF1A5402AE}"/>
-    <cellStyle name="Excel Built-in Normal 2" xfId="8" xr:uid="{FBF60C45-F726-E04A-BB02-17DF2E217B64}"/>
-    <cellStyle name="Excel Built-in Normal 2 2" xfId="13" xr:uid="{862F1D0E-328A-414C-B4C1-637883AFDFC5}"/>
-    <cellStyle name="Hyperlink" xfId="9" xr:uid="{21CF2F2F-B58F-B242-BC83-8A9463C046BC}"/>
+    <cellStyle name="Excel Built-in Hyperlink" xfId="10"/>
+    <cellStyle name="Excel Built-in Normal" xfId="3"/>
+    <cellStyle name="Excel Built-in Normal 2" xfId="8"/>
+    <cellStyle name="Excel Built-in Normal 2 2" xfId="13"/>
+    <cellStyle name="Hyperlink" xfId="9"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 4" xfId="5" xr:uid="{4D3F32C4-49E9-3D46-B351-092EA6741B00}"/>
-    <cellStyle name="一般 4 2" xfId="1" xr:uid="{A2F9AD41-A24B-344D-8788-B40BC0F79FE0}"/>
-    <cellStyle name="一般 4 2 2" xfId="6" xr:uid="{89DE2ACF-F1E1-F441-8388-52088142B672}"/>
-    <cellStyle name="一般 4 2 3" xfId="2" xr:uid="{2700D0B0-350C-8F40-9325-292797AB76B9}"/>
-    <cellStyle name="一般 4 2 3 2" xfId="16" xr:uid="{57877BF8-C8AB-5448-8E14-0CD82E9A66DE}"/>
-    <cellStyle name="一般 5" xfId="7" xr:uid="{89C68155-A896-2D44-9430-43B87D01B84D}"/>
-    <cellStyle name="一般 6" xfId="11" xr:uid="{A2B6B70D-E800-F64D-ABFF-66DA93BF1829}"/>
-    <cellStyle name="一般 6 2" xfId="12" xr:uid="{4677C66A-7057-E04B-9ACA-6C14535450A7}"/>
-    <cellStyle name="一般 7" xfId="4" xr:uid="{F77E584A-4EB8-5A4E-ACD6-DAC483004787}"/>
-    <cellStyle name="一般 7 2" xfId="17" xr:uid="{436B4A5D-4D1D-EC4B-A685-255581283B53}"/>
-    <cellStyle name="一般 7 3" xfId="18" xr:uid="{DE33E3F1-2FA9-124F-B55E-8F3E4BB61D16}"/>
-    <cellStyle name="一般 7 5" xfId="15" xr:uid="{2F8D0BCD-8035-A94E-AF24-5DF2EA3324C9}"/>
+    <cellStyle name="一般 4" xfId="5"/>
+    <cellStyle name="一般 4 2" xfId="1"/>
+    <cellStyle name="一般 4 2 2" xfId="6"/>
+    <cellStyle name="一般 4 2 3" xfId="2"/>
+    <cellStyle name="一般 4 2 3 2" xfId="16"/>
+    <cellStyle name="一般 5" xfId="7"/>
+    <cellStyle name="一般 6" xfId="11"/>
+    <cellStyle name="一般 6 2" xfId="12"/>
+    <cellStyle name="一般 7" xfId="4"/>
+    <cellStyle name="一般 7 2" xfId="17"/>
+    <cellStyle name="一般 7 3" xfId="18"/>
+    <cellStyle name="一般 7 5" xfId="15"/>
     <cellStyle name="千分位" xfId="14" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6425,14 +6468,14 @@
         <xdr:cNvPr id="2" name="影像 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8288B1D-36AA-E249-92C4-DAAF315C5134}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F8288B1D-36AA-E249-92C4-DAAF315C5134}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -6468,14 +6511,14 @@
         <xdr:cNvPr id="3" name="影像 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77225105-5054-EC4C-8623-A30AAA50E535}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{77225105-5054-EC4C-8623-A30AAA50E535}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -6511,14 +6554,14 @@
         <xdr:cNvPr id="4" name="影像 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBCC16F-6A6D-644F-8DC0-84A7CEDF2086}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3BBCC16F-6A6D-644F-8DC0-84A7CEDF2086}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -6582,7 +6625,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -6634,7 +6677,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -6848,43 +6891,43 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2089045E-D400-CB41-AC4F-E6D738664DAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
     <col min="3" max="3" width="74" style="18" customWidth="1"/>
-    <col min="4" max="4" width="67.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="67.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" style="18" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7" ht="39.6">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -6907,72 +6950,72 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="126">
+    <row r="3" spans="1:7" ht="118.8">
       <c r="A3" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G3" s="27" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105">
+    <row r="4" spans="1:7" ht="99">
       <c r="A4" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G4" s="27" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="105">
+    <row r="5" spans="1:7" ht="99">
       <c r="A5" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="121" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="123" customFormat="1" ht="20">
+    <row r="6" spans="1:7" s="123" customFormat="1" ht="19.8">
       <c r="A6" s="135" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B6" s="136"/>
       <c r="C6" s="136"/>
@@ -6981,665 +7024,665 @@
       <c r="F6" s="122"/>
       <c r="G6" s="122"/>
     </row>
-    <row r="7" spans="1:7" ht="21">
+    <row r="7" spans="1:7" ht="19.8">
       <c r="A7" s="124" t="s">
+        <v>368</v>
+      </c>
+      <c r="B7" s="125" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="125" t="s">
         <v>370</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="D7" s="125" t="s">
         <v>371</v>
       </c>
-      <c r="C7" s="125" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="19.8">
+      <c r="A8" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="D7" s="125" t="s">
+      <c r="B8" s="126" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="21">
-      <c r="A8" s="16" t="s">
+      <c r="C8" s="126" t="s">
         <v>374</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="D8" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="126" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="19.8">
+      <c r="A9" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="126" t="s">
+      <c r="B9" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.8">
+      <c r="A10" s="16" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="21">
-      <c r="A9" s="16" t="s">
+      <c r="B10" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C10" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D10" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.8">
+      <c r="A11" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="B9" s="126" t="s">
+      <c r="B11" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" s="126" t="s">
+        <v>379</v>
+      </c>
+      <c r="D11" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C9" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D9" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="21">
-      <c r="A10" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="B10" s="126" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="19.8">
+      <c r="A12" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B12" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D12" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C10" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="21">
-      <c r="A11" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="B11" s="126" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="19.8">
+      <c r="A13" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C13" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D13" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C11" s="126" t="s">
-        <v>381</v>
-      </c>
-      <c r="D11" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="21">
-      <c r="A12" s="16" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="19.8">
+      <c r="A14" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="B12" s="126" t="s">
+      <c r="B14" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C14" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D14" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D12" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="21">
-      <c r="A13" s="16" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="19.8">
+      <c r="A15" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="B13" s="126" t="s">
+      <c r="B15" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C15" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D15" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C13" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D13" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="21">
-      <c r="A14" s="16" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="19.8">
+      <c r="A16" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="B14" s="126" t="s">
+      <c r="B16" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D16" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C14" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D14" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="21">
-      <c r="A15" s="16" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="19.8">
+      <c r="A17" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="B15" s="126" t="s">
+      <c r="B17" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D17" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C15" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D15" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="21">
-      <c r="A16" s="16" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="19.8">
+      <c r="A18" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B16" s="126" t="s">
+      <c r="B18" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C18" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D18" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D16" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="21">
-      <c r="A17" s="16" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="19.8">
+      <c r="A19" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B17" s="126" t="s">
+      <c r="B19" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C17" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D17" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="21">
-      <c r="A18" s="16" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="19.8">
+      <c r="A20" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="B18" s="126" t="s">
+      <c r="B20" s="126" t="s">
+        <v>389</v>
+      </c>
+      <c r="C20" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C18" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D18" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="21">
-      <c r="A19" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="B19" s="126" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="19.8">
+      <c r="A21" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="B21" s="126" t="s">
+        <v>391</v>
+      </c>
+      <c r="C21" s="126" t="s">
+        <v>392</v>
+      </c>
+      <c r="D21" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C19" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D19" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="21">
-      <c r="A20" s="16" t="s">
-        <v>390</v>
-      </c>
-      <c r="B20" s="126" t="s">
-        <v>391</v>
-      </c>
-      <c r="C20" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="21">
-      <c r="A21" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="B21" s="126" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="19.8">
+      <c r="A22" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="C21" s="126" t="s">
+      <c r="B22" s="126" t="s">
         <v>394</v>
       </c>
-      <c r="D21" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="21">
-      <c r="A22" s="16" t="s">
+      <c r="C22" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D22" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="19.8">
+      <c r="A23" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="B22" s="126" t="s">
+      <c r="B23" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C23" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D23" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="19.8">
+      <c r="A24" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="C22" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D22" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="21">
-      <c r="A23" s="16" t="s">
+      <c r="B24" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D24" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="19.8">
+      <c r="A25" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="B23" s="126" t="s">
+      <c r="B25" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D25" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C23" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D23" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="21">
-      <c r="A24" s="16" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="19.8">
+      <c r="A26" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="B24" s="126" t="s">
+      <c r="B26" s="126" t="s">
+        <v>399</v>
+      </c>
+      <c r="C26" s="126" t="s">
+        <v>400</v>
+      </c>
+      <c r="D26" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C24" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D24" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="21">
-      <c r="A25" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="B25" s="126" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="19.8">
+      <c r="A27" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D27" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D25" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="21">
-      <c r="A26" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="B26" s="126" t="s">
-        <v>401</v>
-      </c>
-      <c r="C26" s="126" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="19.8">
+      <c r="A28" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="D26" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="21">
-      <c r="A27" s="16" t="s">
+      <c r="B28" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C28" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D28" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="19.8">
+      <c r="A29" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B29" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C29" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D29" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C27" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="21">
-      <c r="A28" s="16" t="s">
+    </row>
+    <row r="30" spans="1:4" ht="19.8">
+      <c r="A30" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="B28" s="126" t="s">
+      <c r="B30" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C30" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D30" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C28" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D28" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="21">
-      <c r="A29" s="16" t="s">
+    </row>
+    <row r="31" spans="1:4" ht="19.8">
+      <c r="A31" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B31" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D31" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C29" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D29" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="21">
-      <c r="A30" s="16" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="19.8">
+      <c r="A32" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="B30" s="126" t="s">
+      <c r="B32" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C32" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D32" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C30" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D30" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="21">
-      <c r="A31" s="16" t="s">
+    </row>
+    <row r="33" spans="1:4" ht="19.8">
+      <c r="A33" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="B33" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D33" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C31" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D31" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="21">
-      <c r="A32" s="16" t="s">
+    </row>
+    <row r="34" spans="1:4" ht="19.8">
+      <c r="A34" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="B32" s="126" t="s">
+      <c r="B34" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D34" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C32" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D32" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="21">
-      <c r="A33" s="16" t="s">
+    </row>
+    <row r="35" spans="1:4" ht="19.8">
+      <c r="A35" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="B33" s="126" t="s">
+      <c r="B35" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C35" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D35" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C33" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D33" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="21">
-      <c r="A34" s="16" t="s">
+    </row>
+    <row r="36" spans="1:4" ht="19.8">
+      <c r="A36" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="B34" s="126" t="s">
+      <c r="B36" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C36" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D36" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C34" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D34" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="21">
-      <c r="A35" s="16" t="s">
+    </row>
+    <row r="37" spans="1:4" s="127" customFormat="1" ht="19.8">
+      <c r="A37" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="B35" s="126" t="s">
+      <c r="B37" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C37" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D37" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C35" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D35" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="21">
-      <c r="A36" s="16" t="s">
+    </row>
+    <row r="38" spans="1:4" ht="19.8">
+      <c r="A38" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="B36" s="126" t="s">
+      <c r="B38" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C38" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D38" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C36" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D36" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="127" customFormat="1" ht="21">
-      <c r="A37" s="16" t="s">
+    </row>
+    <row r="39" spans="1:4" ht="19.8">
+      <c r="A39" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="B37" s="126" t="s">
+      <c r="B39" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C39" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D39" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C37" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D37" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="21">
-      <c r="A38" s="16" t="s">
+    </row>
+    <row r="40" spans="1:4" ht="19.8">
+      <c r="A40" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="B38" s="126" t="s">
+      <c r="B40" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C40" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D40" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C38" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D38" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="21">
-      <c r="A39" s="16" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="19.8">
+      <c r="A41" s="16" t="s">
         <v>415</v>
       </c>
-      <c r="B39" s="126" t="s">
+      <c r="B41" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C41" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D41" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C39" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D39" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="21">
-      <c r="A40" s="16" t="s">
+    </row>
+    <row r="42" spans="1:4" ht="19.8">
+      <c r="A42" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="B40" s="126" t="s">
+      <c r="B42" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="126" t="s">
+        <v>417</v>
+      </c>
+      <c r="D42" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C40" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D40" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="21">
-      <c r="A41" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="B41" s="126" t="s">
+    </row>
+    <row r="43" spans="1:4" ht="19.8">
+      <c r="A43" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B43" s="126" t="s">
+        <v>419</v>
+      </c>
+      <c r="C43" s="126" t="s">
+        <v>420</v>
+      </c>
+      <c r="D43" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C41" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D41" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="21">
-      <c r="A42" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="B42" s="126" t="s">
-        <v>396</v>
-      </c>
-      <c r="C42" s="126" t="s">
-        <v>419</v>
-      </c>
-      <c r="D42" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="21">
-      <c r="A43" s="16" t="s">
-        <v>420</v>
-      </c>
-      <c r="B43" s="126" t="s">
+    </row>
+    <row r="44" spans="1:4" ht="19.8">
+      <c r="A44" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="C43" s="126" t="s">
+      <c r="B44" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C44" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D44" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="19.8">
+      <c r="A45" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="D43" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="21">
-      <c r="A44" s="16" t="s">
+      <c r="B45" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D45" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="19.8">
+      <c r="A46" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="B44" s="126" t="s">
+      <c r="B46" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C46" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D46" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C44" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D44" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="21">
-      <c r="A45" s="16" t="s">
+    </row>
+    <row r="47" spans="1:4" ht="19.8">
+      <c r="A47" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="B45" s="126" t="s">
+      <c r="B47" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D47" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C45" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D45" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="21">
-      <c r="A46" s="16" t="s">
+    </row>
+    <row r="48" spans="1:4" ht="19.8">
+      <c r="A48" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="B46" s="126" t="s">
+      <c r="B48" s="126" t="s">
+        <v>373</v>
+      </c>
+      <c r="C48" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D48" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C46" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D46" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="21">
-      <c r="A47" s="16" t="s">
+    </row>
+    <row r="49" spans="1:4" ht="19.8">
+      <c r="A49" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="B47" s="126" t="s">
+      <c r="B49" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C49" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D49" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C47" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D47" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="21">
-      <c r="A48" s="16" t="s">
+    </row>
+    <row r="50" spans="1:4" ht="19.8">
+      <c r="A50" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="B48" s="126" t="s">
+      <c r="B50" s="126" t="s">
+        <v>428</v>
+      </c>
+      <c r="C50" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D50" s="126" t="s">
         <v>375</v>
       </c>
-      <c r="C48" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D48" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="21">
-      <c r="A49" s="16" t="s">
+    </row>
+    <row r="51" spans="1:4" ht="19.8">
+      <c r="A51" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="B51" s="126" t="s">
         <v>428</v>
       </c>
-      <c r="B49" s="126" t="s">
-        <v>396</v>
-      </c>
-      <c r="C49" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D49" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="21">
-      <c r="A50" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B50" s="126" t="s">
+      <c r="C51" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D51" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="19.8">
+      <c r="A52" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="C50" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D50" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="21">
-      <c r="A51" s="16" t="s">
+      <c r="B52" s="128" t="s">
+        <v>428</v>
+      </c>
+      <c r="C52" s="126" t="s">
+        <v>374</v>
+      </c>
+      <c r="D52" s="126" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="19.8">
+      <c r="A53" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="B51" s="126" t="s">
-        <v>430</v>
-      </c>
-      <c r="C51" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D51" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="21">
-      <c r="A52" s="16" t="s">
+      <c r="B53" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C53" s="126" t="s">
         <v>432</v>
       </c>
-      <c r="B52" s="128" t="s">
-        <v>430</v>
-      </c>
-      <c r="C52" s="126" t="s">
-        <v>376</v>
-      </c>
-      <c r="D52" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="21">
-      <c r="A53" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="B53" s="126" t="s">
-        <v>396</v>
-      </c>
-      <c r="C53" s="126" t="s">
-        <v>434</v>
-      </c>
       <c r="D53" s="126" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="20">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="19.8">
       <c r="B54" s="129"/>
     </row>
   </sheetData>
@@ -7648,22 +7691,23 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9FB726-8E70-0940-98D3-EF2918032583}">
-  <dimension ref="A1:L1048576"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.6640625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="34" style="20" customWidth="1"/>
-    <col min="2" max="2" width="28.5" style="20" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" style="20" customWidth="1"/>
     <col min="3" max="3" width="63" style="20" customWidth="1"/>
-    <col min="4" max="4" width="64.5" style="20" customWidth="1"/>
+    <col min="4" max="4" width="64.44140625" style="20" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" style="20" customWidth="1"/>
     <col min="6" max="10" width="9.6640625" style="20"/>
-    <col min="11" max="11" width="12.1640625" style="20" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="20" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="20" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" style="20" customWidth="1"/>
     <col min="13" max="16384" width="9.6640625" style="20"/>
   </cols>
   <sheetData>
@@ -7674,7 +7718,7 @@
       <c r="B1" s="77"/>
       <c r="C1" s="77"/>
       <c r="D1" s="77" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E1" s="77"/>
       <c r="F1" s="78"/>
@@ -7694,10 +7738,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="78" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="78" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G2" s="78" t="s">
         <v>4</v>
@@ -7708,17 +7752,17 @@
         <v>25</v>
       </c>
       <c r="B3" s="78" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>184</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>186</v>
       </c>
       <c r="E3" s="78"/>
       <c r="F3" s="78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G3" s="78"/>
     </row>
@@ -7727,32 +7771,32 @@
         <v>25</v>
       </c>
       <c r="B4" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="79" t="s">
         <v>188</v>
-      </c>
-      <c r="C4" s="79" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="79" t="s">
-        <v>190</v>
       </c>
       <c r="E4" s="78"/>
       <c r="F4" s="78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G4" s="78"/>
     </row>
-    <row r="5" spans="1:12" ht="161.5" customHeight="1">
+    <row r="5" spans="1:12" ht="161.55000000000001" customHeight="1">
       <c r="A5" s="78" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -7760,16 +7804,16 @@
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1">
       <c r="H6" s="80" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I6" s="80" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J6" s="80" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K6" s="80" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L6" s="80" t="s">
         <v>0</v>
@@ -7787,9 +7831,9 @@
       </c>
       <c r="L7" s="80"/>
     </row>
-    <row r="8" spans="1:12" ht="20">
+    <row r="8" spans="1:12" ht="19.8">
       <c r="H8" s="80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I8" s="80">
         <v>0</v>
@@ -7800,9 +7844,6 @@
       <c r="K8" s="80"/>
       <c r="L8" s="80"/>
     </row>
-    <row r="1048574" s="20" customFormat="1"/>
-    <row r="1048575" s="20" customFormat="1"/>
-    <row r="1048576" s="20" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7810,30 +7851,30 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39581882-709E-504F-82CA-2906F05A6AAC}">
-  <dimension ref="A1:I48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20.33203125" style="83" customWidth="1"/>
-    <col min="2" max="2" width="51.5" style="83" customWidth="1"/>
+    <col min="2" max="2" width="51.44140625" style="83" customWidth="1"/>
     <col min="3" max="3" width="48.33203125" style="83" customWidth="1"/>
-    <col min="4" max="4" width="74.5" style="83" customWidth="1"/>
+    <col min="4" max="4" width="74.44140625" style="83" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" style="83" customWidth="1"/>
-    <col min="6" max="6" width="27.1640625" style="83" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" style="83" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="83" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" style="83" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" style="83" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" style="83" customWidth="1"/>
-    <col min="10" max="16384" width="7.5" style="83"/>
+    <col min="10" max="16384" width="7.44140625" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42">
+    <row r="1" spans="1:9" ht="39.6">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -7841,7 +7882,7 @@
       <c r="H1" s="82"/>
       <c r="I1" s="82"/>
     </row>
-    <row r="2" spans="1:9" ht="21">
+    <row r="2" spans="1:9" ht="19.8">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7861,152 +7902,152 @@
         <v>39</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="I2" s="84" t="s">
         <v>198</v>
       </c>
-      <c r="H2" s="84" t="s">
+    </row>
+    <row r="3" spans="1:9" s="85" customFormat="1" ht="161.55000000000001" customHeight="1">
+      <c r="A3" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="C3" s="19" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="85" customFormat="1" ht="161.5" customHeight="1">
-      <c r="A3" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="D3" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="E3" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F3" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="G3" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="F3" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
     </row>
-    <row r="4" spans="1:9" s="85" customFormat="1" ht="161.5" customHeight="1">
+    <row r="4" spans="1:9" s="85" customFormat="1" ht="161.55000000000001" customHeight="1">
       <c r="A4" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="44" t="s">
+      <c r="F4" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
     </row>
-    <row r="5" spans="1:9" s="85" customFormat="1" ht="161.5" customHeight="1">
+    <row r="5" spans="1:9" s="85" customFormat="1" ht="161.55000000000001" customHeight="1">
       <c r="A5" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="E5" s="44" t="s">
+      <c r="G5" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="85" customFormat="1" ht="161.55000000000001" customHeight="1">
+      <c r="A6" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" s="85" customFormat="1" ht="161.5" customHeight="1">
-      <c r="A6" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="44" t="s">
+      <c r="D6" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="E6" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="44" t="s">
+      <c r="G6" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="H6" s="86"/>
       <c r="I6" s="44" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="85" customFormat="1" ht="409.5" customHeight="1">
       <c r="A7" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="G7" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="G7" s="44" t="s">
-        <v>206</v>
       </c>
       <c r="H7" s="87"/>
       <c r="I7" s="44"/>
     </row>
     <row r="8" spans="1:9" ht="70.5" customHeight="1">
       <c r="A8" s="147" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B8" s="88"/>
       <c r="C8" s="89"/>
       <c r="D8" s="149" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="70.5" customHeight="1">
@@ -8023,25 +8064,25 @@
     </row>
     <row r="11" spans="1:9" ht="70.5" customHeight="1">
       <c r="A11" s="147" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="89" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="D11" s="149" t="s">
         <v>225</v>
-      </c>
-      <c r="C11" s="89" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="149" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="70.5" customHeight="1">
       <c r="A12" s="148"/>
       <c r="B12" s="88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C12" s="89" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D12" s="150"/>
     </row>
@@ -8051,38 +8092,6 @@
       <c r="C13" s="91"/>
       <c r="D13" s="151"/>
     </row>
-    <row r="17" s="83" customFormat="1"/>
-    <row r="18" s="83" customFormat="1"/>
-    <row r="19" s="83" customFormat="1"/>
-    <row r="20" s="83" customFormat="1"/>
-    <row r="21" s="83" customFormat="1"/>
-    <row r="22" s="83" customFormat="1"/>
-    <row r="23" s="83" customFormat="1"/>
-    <row r="24" s="83" customFormat="1"/>
-    <row r="25" s="83" customFormat="1"/>
-    <row r="26" s="83" customFormat="1"/>
-    <row r="27" s="83" customFormat="1"/>
-    <row r="28" s="83" customFormat="1"/>
-    <row r="29" s="83" customFormat="1"/>
-    <row r="30" s="83" customFormat="1"/>
-    <row r="31" s="83" customFormat="1"/>
-    <row r="32" s="83" customFormat="1"/>
-    <row r="33" s="83" customFormat="1"/>
-    <row r="34" s="83" customFormat="1"/>
-    <row r="35" s="83" customFormat="1"/>
-    <row r="36" s="83" customFormat="1"/>
-    <row r="37" s="83" customFormat="1"/>
-    <row r="38" s="83" customFormat="1"/>
-    <row r="39" s="83" customFormat="1"/>
-    <row r="40" s="83" customFormat="1"/>
-    <row r="41" s="83" customFormat="1"/>
-    <row r="42" s="83" customFormat="1"/>
-    <row r="43" s="83" customFormat="1"/>
-    <row r="44" s="83" customFormat="1"/>
-    <row r="45" s="83" customFormat="1"/>
-    <row r="46" s="83" customFormat="1"/>
-    <row r="47" s="83" customFormat="1"/>
-    <row r="48" s="83" customFormat="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A8:A10"/>
@@ -8096,35 +8105,35 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3003D53-D28C-F841-8AF9-2CD3FDD1D95F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
-    <col min="3" max="3" width="70.83203125" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="70.77734375" style="18" customWidth="1"/>
     <col min="4" max="4" width="70" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" style="18" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" style="18" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="18" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="18" customWidth="1"/>
     <col min="9" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7" ht="39.6">
       <c r="A1" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8152,105 +8161,105 @@
         <v>5</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="E3" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="14" t="s">
         <v>232</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>234</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="138.5" customHeight="1">
+    <row r="4" spans="1:7" ht="138.44999999999999" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="138.5" customHeight="1">
+    <row r="5" spans="1:7" ht="138.44999999999999" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="112.75" customHeight="1">
+    <row r="6" spans="1:7" ht="112.8" customHeight="1">
       <c r="A6" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="92" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="D6" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="E6" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="14" t="s">
         <v>242</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>244</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="126">
+    <row r="7" spans="1:7" ht="118.8">
       <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="93" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="93" t="s">
         <v>245</v>
-      </c>
-      <c r="C7" s="93" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="93" t="s">
-        <v>247</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
@@ -8263,36 +8272,36 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B58BCC1-88B7-064C-8D15-03D3E59397A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="74" style="18" customWidth="1"/>
-    <col min="4" max="4" width="67.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="67.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22">
+    <row r="1" spans="1:7" ht="36">
       <c r="A1" s="94" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
       <c r="D1" s="94" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="94"/>
       <c r="F1" s="94"/>
       <c r="G1" s="94"/>
     </row>
-    <row r="2" spans="1:7" s="96" customFormat="1" ht="22">
+    <row r="2" spans="1:7" s="96" customFormat="1">
       <c r="A2" s="95" t="s">
         <v>0</v>
       </c>
@@ -8316,101 +8325,101 @@
       </c>
     </row>
     <row r="3" spans="1:7" hidden="1"/>
-    <row r="4" spans="1:7" ht="220">
+    <row r="4" spans="1:7" ht="180">
       <c r="A4" s="97" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="97" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="98" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="E4" s="97" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="98" t="s">
+      <c r="F4" s="97" t="s">
         <v>251</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="G4" s="98" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="97" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="90">
+      <c r="A5" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="99" t="s">
         <v>253</v>
-      </c>
-      <c r="G4" s="98" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="110">
-      <c r="A5" s="99" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="99" t="s">
-        <v>255</v>
       </c>
       <c r="C5" s="98"/>
       <c r="D5" s="100" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E5" s="97"/>
       <c r="F5" s="97" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="98"/>
+    </row>
+    <row r="6" spans="1:7" ht="72">
+      <c r="A6" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="99" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="100" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="98"/>
-    </row>
-    <row r="6" spans="1:7" ht="88">
-      <c r="A6" s="99" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="99" t="s">
+      <c r="D6" s="100" t="s">
         <v>258</v>
-      </c>
-      <c r="C6" s="100" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="100" t="s">
-        <v>260</v>
       </c>
       <c r="E6" s="99"/>
       <c r="F6" s="99" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="100"/>
+    </row>
+    <row r="7" spans="1:7" hidden="1">
+      <c r="A7" s="152" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="102" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="100"/>
-    </row>
-    <row r="7" spans="1:7" ht="22" hidden="1">
-      <c r="A7" s="152" t="s">
+      <c r="C7" s="102" t="s">
         <v>262</v>
       </c>
-      <c r="B7" s="102" t="s">
-        <v>263</v>
-      </c>
-      <c r="C7" s="102" t="s">
-        <v>264</v>
-      </c>
       <c r="D7" s="102" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E7" s="101"/>
       <c r="F7" s="101"/>
       <c r="G7" s="102"/>
     </row>
-    <row r="8" spans="1:7" ht="22" hidden="1">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" s="152"/>
       <c r="B8" s="102" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C8" s="102" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D8" s="102" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E8" s="101"/>
       <c r="F8" s="101"/>
       <c r="G8" s="102"/>
     </row>
-    <row r="9" spans="1:7" ht="22" hidden="1">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="152"/>
       <c r="B9" s="102" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C9" s="103">
         <v>0.2</v>
@@ -8422,10 +8431,10 @@
       <c r="F9" s="101"/>
       <c r="G9" s="102"/>
     </row>
-    <row r="10" spans="1:7" ht="22" hidden="1">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" s="152"/>
       <c r="B10" s="102" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C10" s="103">
         <v>0.2</v>
@@ -8439,7 +8448,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="104" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B11" s="105"/>
       <c r="C11" s="105"/>
@@ -8448,92 +8457,92 @@
       <c r="F11" s="105"/>
       <c r="G11" s="105"/>
     </row>
-    <row r="12" spans="1:7" s="105" customFormat="1" ht="66">
+    <row r="12" spans="1:7" s="105" customFormat="1" ht="54">
       <c r="A12" s="106" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B12" s="106" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="107" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="107" t="s">
+        <v>269</v>
+      </c>
+      <c r="E12" s="106" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="F12" s="106" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="107" t="s">
-        <v>271</v>
-      </c>
-      <c r="E12" s="106" t="s">
+      <c r="G12" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="F12" s="106" t="s">
+    </row>
+    <row r="13" spans="1:7" s="105" customFormat="1" ht="72">
+      <c r="A13" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="108" t="s">
         <v>273</v>
       </c>
-      <c r="G12" s="107" t="s">
+      <c r="C13" s="109" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" s="105" customFormat="1" ht="88">
-      <c r="A13" s="108" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="108" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13" s="109" t="s">
-        <v>276</v>
-      </c>
       <c r="D13" s="109" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E13" s="108"/>
       <c r="F13" s="108" t="s">
+        <v>275</v>
+      </c>
+      <c r="G13" s="109"/>
+    </row>
+    <row r="14" spans="1:7" s="105" customFormat="1" ht="72">
+      <c r="A14" s="106" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="106" t="s">
         <v>277</v>
       </c>
-      <c r="G13" s="109"/>
-    </row>
-    <row r="14" spans="1:7" s="105" customFormat="1" ht="88">
-      <c r="A14" s="106" t="s">
+      <c r="C14" s="110" t="s">
         <v>278</v>
       </c>
-      <c r="B14" s="106" t="s">
+      <c r="D14" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" s="111" t="s">
         <v>279</v>
       </c>
-      <c r="C14" s="110" t="s">
+      <c r="F14" s="111" t="s">
         <v>280</v>
       </c>
-      <c r="D14" s="110" t="s">
-        <v>280</v>
-      </c>
-      <c r="E14" s="111" t="s">
+      <c r="G14" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="F14" s="111" t="s">
+    </row>
+    <row r="15" spans="1:7" s="105" customFormat="1" ht="72">
+      <c r="A15" s="111" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="112" t="s">
         <v>282</v>
       </c>
-      <c r="G14" s="110" t="s">
+      <c r="C15" s="110" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" s="105" customFormat="1" ht="88">
-      <c r="A15" s="111" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="112" t="s">
+      <c r="D15" s="110" t="s">
         <v>284</v>
       </c>
-      <c r="C15" s="110" t="s">
+      <c r="E15" s="113" t="s">
         <v>285</v>
       </c>
-      <c r="D15" s="110" t="s">
+      <c r="F15" s="113" t="s">
+        <v>271</v>
+      </c>
+      <c r="G15" s="114" t="s">
         <v>286</v>
-      </c>
-      <c r="E15" s="113" t="s">
-        <v>287</v>
-      </c>
-      <c r="F15" s="113" t="s">
-        <v>273</v>
-      </c>
-      <c r="G15" s="114" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -8546,36 +8555,36 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B8896C-1E14-E147-AD80-5D134BBDEEEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="39.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
-    <col min="3" max="3" width="64.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="80.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="64.77734375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="80.44140625" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="26.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21">
+    <row r="1" spans="1:21" ht="19.8">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:21" ht="21">
+    <row r="2" spans="1:21" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8598,7 +8607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="273">
+    <row r="3" spans="1:21" ht="316.8">
       <c r="A3" s="14" t="s">
         <v>25</v>
       </c>
@@ -8606,45 +8615,45 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="210">
+    <row r="4" spans="1:21" ht="237.6">
       <c r="A4" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="147">
+    <row r="5" spans="1:21" ht="158.4">
       <c r="A5" s="14" t="s">
         <v>25</v>
       </c>
@@ -8652,91 +8661,91 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="168">
+    <row r="6" spans="1:21" ht="198">
       <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="126">
+    <row r="7" spans="1:21" ht="118.8">
       <c r="A7" s="115" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="158.4">
+      <c r="A8" s="115" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="126">
-      <c r="A8" s="115" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="63">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="59.4">
       <c r="A9" s="14" t="s">
         <v>25</v>
       </c>
@@ -8744,39 +8753,39 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:21" ht="105">
+    <row r="10" spans="1:21" ht="99">
       <c r="A10" s="14"/>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:21" s="13" customFormat="1" ht="33">
+    <row r="11" spans="1:21" s="13" customFormat="1" ht="28.8">
       <c r="A11" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -8799,22 +8808,22 @@
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
     </row>
-    <row r="12" spans="1:21" s="119" customFormat="1" ht="357">
+    <row r="12" spans="1:21" s="119" customFormat="1" ht="352.8" customHeight="1">
       <c r="A12" s="116"/>
       <c r="B12" s="117"/>
       <c r="C12" s="118" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E12" s="117"/>
       <c r="F12" s="117"/>
       <c r="G12" s="117"/>
     </row>
-    <row r="13" spans="1:21" s="13" customFormat="1" ht="33">
+    <row r="13" spans="1:21" s="13" customFormat="1" ht="28.8">
       <c r="A13" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -8837,72 +8846,72 @@
       <c r="T13" s="10"/>
       <c r="U13" s="10"/>
     </row>
-    <row r="14" spans="1:21" ht="126">
+    <row r="14" spans="1:21" ht="118.8">
       <c r="A14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="120" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="E14" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:21" ht="99">
+      <c r="A15" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:21" ht="105">
-      <c r="A15" s="14" t="s">
+      <c r="C15" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:21" ht="84">
+    <row r="16" spans="1:21" ht="79.2">
       <c r="A16" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" s="13" customFormat="1" ht="33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" s="13" customFormat="1" ht="28.8">
       <c r="A19" s="10" t="s">
         <v>21</v>
       </c>
@@ -8927,18 +8936,18 @@
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
     </row>
-    <row r="20" spans="1:21" ht="126">
+    <row r="20" spans="1:21" ht="158.4">
       <c r="A20" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>23</v>
@@ -8950,7 +8959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="126">
+    <row r="21" spans="1:21" ht="118.8">
       <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
@@ -8958,56 +8967,56 @@
         <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="126">
+    <row r="22" spans="1:21" ht="118.8">
       <c r="A22" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:21" ht="126">
+    <row r="23" spans="1:21" ht="138.6">
       <c r="A23" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="105">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="99">
       <c r="A24" s="14" t="s">
         <v>16</v>
       </c>
@@ -9015,33 +9024,33 @@
         <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="105">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="99">
       <c r="A25" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -9054,22 +9063,22 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1226C5AD-D9E7-1144-984A-B0AAE84B85B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
     <col min="3" max="3" width="74" style="18" customWidth="1"/>
-    <col min="4" max="4" width="67.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="67.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="18" style="18" customWidth="1"/>
-    <col min="6" max="6" width="8.1640625" style="18" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="18" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="18" customWidth="1"/>
     <col min="9" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="42">
+    <row r="1" spans="1:6" ht="59.4">
       <c r="A1" s="3" t="s">
         <v>472</v>
       </c>
@@ -9079,7 +9088,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" ht="20">
+    <row r="2" spans="1:6" ht="19.8">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9087,7 +9096,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" ht="20">
+    <row r="3" spans="1:6" ht="19.8">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9095,7 +9104,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="20">
+    <row r="4" spans="1:6" ht="19.8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9103,7 +9112,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="14"/>
     </row>
-    <row r="5" spans="1:6" ht="20">
+    <row r="5" spans="1:6" ht="19.8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9111,7 +9120,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="20">
+    <row r="6" spans="1:6" ht="19.8">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9119,7 +9128,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" ht="21">
+    <row r="7" spans="1:6" ht="19.8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="15"/>
@@ -9127,7 +9136,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" ht="21">
+    <row r="8" spans="1:6" ht="19.8">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -9135,7 +9144,7 @@
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:6" ht="21">
+    <row r="9" spans="1:6" ht="19.8">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9143,7 +9152,7 @@
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:6" ht="21">
+    <row r="10" spans="1:6" ht="19.8">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -9154,40 +9163,41 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23291D27-F562-8248-A41B-FEFF83B9833D}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" style="18" customWidth="1"/>
     <col min="3" max="3" width="74" style="18" customWidth="1"/>
-    <col min="4" max="4" width="67.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="67.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" style="18" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7" ht="39.6">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -9212,19 +9222,19 @@
     </row>
     <row r="3" spans="1:7" ht="189" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" s="132" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="133" t="s">
+        <v>459</v>
+      </c>
+      <c r="D3" s="133" t="s">
+        <v>468</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>460</v>
-      </c>
-      <c r="C3" s="133" t="s">
-        <v>461</v>
-      </c>
-      <c r="D3" s="133" t="s">
-        <v>471</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>462</v>
       </c>
       <c r="F3" s="134"/>
       <c r="G3" s="3" t="s">
@@ -9233,19 +9243,19 @@
     </row>
     <row r="4" spans="1:7" ht="195" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" s="132" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C4" s="133" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D4" s="133" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>11</v>
@@ -9256,45 +9266,72 @@
         <v>40</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F5" s="134" t="s">
         <v>465</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="F5" s="134" t="s">
-        <v>468</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:7" ht="19.8">
+      <c r="A6" s="135" t="s">
+        <v>367</v>
+      </c>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+    </row>
+    <row r="7" spans="1:7" ht="19.8">
+      <c r="A7" s="124" t="s">
+        <v>368</v>
+      </c>
+      <c r="B7" s="125" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.8">
+      <c r="A8" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="B8" s="153" t="s">
+        <v>476</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A0F767-E715-7B42-A364-FE803579BF93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="34.5" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" customWidth="1"/>
     <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="75.5" customWidth="1"/>
-    <col min="4" max="4" width="115.5" customWidth="1"/>
-    <col min="5" max="5" width="38.1640625" customWidth="1"/>
+    <col min="3" max="3" width="75.44140625" customWidth="1"/>
+    <col min="4" max="4" width="115.44140625" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" customWidth="1"/>
     <col min="6" max="6" width="27.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21">
+    <row r="1" spans="1:7" ht="19.8">
       <c r="A1" s="27" t="s">
         <v>33</v>
       </c>
@@ -9307,7 +9344,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
@@ -9330,7 +9367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="210">
+    <row r="3" spans="1:7" ht="198">
       <c r="A3" s="28" t="s">
         <v>40</v>
       </c>
@@ -9344,35 +9381,35 @@
         <v>43</v>
       </c>
       <c r="E3" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>45</v>
       </c>
       <c r="G3" s="27" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="273">
+    <row r="4" spans="1:7" ht="257.39999999999998">
       <c r="A4" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="27" t="s">
-        <v>49</v>
+        <v>470</v>
       </c>
       <c r="G4" s="27"/>
     </row>
-    <row r="5" spans="1:7" ht="20">
+    <row r="5" spans="1:7" ht="19.8">
       <c r="A5" s="31"/>
       <c r="B5" s="32"/>
       <c r="C5" s="33"/>
@@ -9381,7 +9418,7 @@
       <c r="F5" s="34"/>
       <c r="G5" s="35"/>
     </row>
-    <row r="6" spans="1:7" ht="20">
+    <row r="6" spans="1:7" ht="19.8">
       <c r="A6" s="36"/>
       <c r="B6" s="37"/>
       <c r="C6" s="38"/>
@@ -9399,24 +9436,24 @@
       <c r="F7" s="39"/>
       <c r="G7" s="39"/>
     </row>
-    <row r="8" spans="1:7" ht="168">
+    <row r="8" spans="1:7" ht="158.4">
       <c r="A8" s="40" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="E8" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>53</v>
       </c>
       <c r="G8" s="42" t="s">
         <v>11</v>
@@ -9425,41 +9462,42 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C040D364-CE28-6A4B-9BFE-EB519BDD6749}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.8"/>
   <cols>
-    <col min="1" max="1" width="20.5" style="43" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="43" customWidth="1"/>
     <col min="2" max="2" width="21" style="43" customWidth="1"/>
-    <col min="3" max="3" width="93.5" style="43" customWidth="1"/>
-    <col min="4" max="4" width="94.5" style="43" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="43" customWidth="1"/>
+    <col min="3" max="3" width="93.44140625" style="43" customWidth="1"/>
+    <col min="4" max="4" width="94.44140625" style="43" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" style="43" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" style="43" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="43" customWidth="1"/>
     <col min="8" max="8" width="39.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="43" customWidth="1"/>
     <col min="10" max="16384" width="9" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="42">
+    <row r="1" spans="1:8" ht="39.6">
       <c r="A1" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
       <c r="D1" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
       <c r="H1" s="25"/>
     </row>
-    <row r="2" spans="1:8" ht="21">
+    <row r="2" spans="1:8">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -9473,10 +9511,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>4</v>
@@ -9485,82 +9523,82 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="210">
+    <row r="3" spans="1:8" ht="198">
       <c r="A3" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="E3" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>59</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>61</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="126">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="118.8">
       <c r="A4" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>65</v>
-      </c>
       <c r="E4" s="22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="294">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="277.2">
       <c r="A5" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>69</v>
-      </c>
       <c r="E5" s="22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -9573,9 +9611,9 @@
       <c r="G6" s="47"/>
       <c r="H6" s="49"/>
     </row>
-    <row r="7" spans="1:8" ht="22.25" customHeight="1">
+    <row r="7" spans="1:8" ht="22.2" customHeight="1">
       <c r="A7" s="138" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="139"/>
       <c r="C7" s="139"/>
@@ -9587,14 +9625,14 @@
     </row>
     <row r="8" spans="1:8" s="51" customFormat="1">
       <c r="A8" s="141" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="141"/>
       <c r="C8" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" s="141"/>
       <c r="F8" s="141"/>
@@ -9603,24 +9641,24 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="52">
         <v>17</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B10" s="52">
         <v>1</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -9636,36 +9674,36 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB69ED1-3D5E-9848-8F78-D062847583C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
     <col min="3" max="3" width="80.6640625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="82.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="82.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" style="18" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7" ht="39.6">
       <c r="A1" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -9688,120 +9726,120 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="378">
+    <row r="3" spans="1:7" ht="376.2">
       <c r="A3" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C3" s="130" t="s">
         <v>437</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="130" t="s">
         <v>438</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="E3" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="F3" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="261">
+      <c r="A4" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="300">
-      <c r="A4" s="14" t="s">
+      <c r="C4" s="131" t="s">
         <v>443</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="131" t="s">
         <v>444</v>
-      </c>
-      <c r="C4" s="131" t="s">
-        <v>445</v>
-      </c>
-      <c r="D4" s="131" t="s">
-        <v>446</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="198">
+      <c r="A5" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="C5" s="130" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="210">
-      <c r="A5" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="130" t="s">
         <v>449</v>
       </c>
-      <c r="C5" s="130" t="s">
+      <c r="E5" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D5" s="130" t="s">
+      <c r="F5" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="138.6">
+      <c r="A6" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="C6" s="130" t="s">
         <v>453</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="147">
-      <c r="A6" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C6" s="130" t="s">
-        <v>455</v>
-      </c>
       <c r="D6" s="130" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="189">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="178.2">
       <c r="A7" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="130" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D7" s="130" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="20">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.8">
       <c r="A8" s="14"/>
       <c r="B8" s="3"/>
       <c r="C8" s="130"/>
@@ -9817,36 +9855,36 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F59A67-5D94-F845-A500-B56249A86486}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="18" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="18" customWidth="1"/>
     <col min="3" max="3" width="45.6640625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="52.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="18" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" style="18" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="18" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="18" customWidth="1"/>
     <col min="10" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42">
+    <row r="1" spans="1:7" ht="39.6">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="21">
+    <row r="2" spans="1:7" ht="19.8">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -9869,79 +9907,79 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="302.5" customHeight="1">
+    <row r="3" spans="1:7" ht="302.55" customHeight="1">
       <c r="A3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="228.5" customHeight="1">
+    <row r="4" spans="1:7" ht="228.45" customHeight="1">
       <c r="A4" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="256.75" customHeight="1">
+    <row r="5" spans="1:7" ht="256.8" customHeight="1">
       <c r="A5" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="227.5" customHeight="1">
+    <row r="6" spans="1:7" ht="227.55" customHeight="1">
       <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -9952,11 +9990,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038FC992-C725-8646-B1F4-DE163A4FCC9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AMJ5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.8"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="52" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="52" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" style="52" customWidth="1"/>
     <col min="3" max="3" width="55.33203125" style="52" customWidth="1"/>
     <col min="4" max="4" width="60.33203125" style="52" customWidth="1"/>
@@ -9966,14 +10004,14 @@
     <col min="10" max="1024" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42">
+    <row r="1" spans="1:9" ht="39.6">
       <c r="A1" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
       <c r="D1" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
@@ -9981,7 +10019,7 @@
       <c r="H1" s="19"/>
       <c r="I1" s="19"/>
     </row>
-    <row r="2" spans="1:9" ht="21">
+    <row r="2" spans="1:9">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -9995,10 +10033,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>4</v>
@@ -10007,27 +10045,27 @@
         <v>24</v>
       </c>
       <c r="I2" s="19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="186.3" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="186.25" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="C3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="D3" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>100</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>11</v>
@@ -10039,18 +10077,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="186.25" customHeight="1">
+    <row r="4" spans="1:9" ht="186.3" customHeight="1">
       <c r="A4" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>102</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>104</v>
       </c>
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
@@ -10063,13 +10101,13 @@
         <v>25</v>
       </c>
       <c r="B5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>107</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>26</v>
@@ -10096,22 +10134,22 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F133481-E5B9-8F4B-B971-355F837E7F3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="43.5" style="8" customWidth="1"/>
-    <col min="2" max="2" width="56.1640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="51.1640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="43.44140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="56.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="51.109375" style="7" customWidth="1"/>
     <col min="4" max="4" width="61" style="7" customWidth="1"/>
     <col min="5" max="5" width="32.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="8" customWidth="1"/>
     <col min="7" max="16384" width="8.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21">
+    <row r="1" spans="1:6" ht="19.8">
       <c r="A1" s="4" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10119,7 +10157,7 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" ht="20">
+    <row r="2" spans="1:6" ht="19.8">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -10127,7 +10165,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="20">
+    <row r="3" spans="1:6" ht="19.8">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -10135,7 +10173,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" s="7" customFormat="1" ht="20">
+    <row r="4" spans="1:6" s="7" customFormat="1" ht="19.8">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -10143,7 +10181,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" s="7" customFormat="1" ht="20">
+    <row r="5" spans="1:6" s="7" customFormat="1" ht="19.8">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -10151,7 +10189,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" s="7" customFormat="1" ht="20">
+    <row r="6" spans="1:6" s="7" customFormat="1" ht="19.8">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -10159,155 +10197,155 @@
       <c r="E6" s="4"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:6" s="7" customFormat="1">
+    <row r="7" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" s="7" customFormat="1">
+    <row r="8" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" s="7" customFormat="1">
+    <row r="9" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" s="7" customFormat="1">
+    <row r="10" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A10" s="8"/>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" s="7" customFormat="1">
+    <row r="11" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" s="7" customFormat="1">
+    <row r="12" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" s="7" customFormat="1">
+    <row r="13" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" s="7" customFormat="1">
+    <row r="14" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" s="7" customFormat="1">
+    <row r="15" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" s="7" customFormat="1">
+    <row r="16" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" s="7" customFormat="1">
+    <row r="17" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" s="7" customFormat="1">
+    <row r="18" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" s="7" customFormat="1">
+    <row r="19" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" s="7" customFormat="1">
+    <row r="20" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" s="7" customFormat="1">
+    <row r="21" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" s="7" customFormat="1">
+    <row r="22" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" s="7" customFormat="1">
+    <row r="23" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" s="7" customFormat="1">
+    <row r="24" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" s="7" customFormat="1">
+    <row r="25" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" s="7" customFormat="1">
+    <row r="26" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" s="7" customFormat="1">
+    <row r="27" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" s="7" customFormat="1">
+    <row r="28" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" s="7" customFormat="1">
+    <row r="29" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" s="7" customFormat="1">
+    <row r="30" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" s="7" customFormat="1">
+    <row r="31" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" s="7" customFormat="1">
+    <row r="32" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:6" s="7" customFormat="1">
+    <row r="33" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" s="7" customFormat="1">
+    <row r="34" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" s="7" customFormat="1">
+    <row r="35" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" s="7" customFormat="1">
+    <row r="36" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" s="7" customFormat="1">
+    <row r="37" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" s="7" customFormat="1">
+    <row r="38" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:6" s="7" customFormat="1">
+    <row r="39" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:6" s="7" customFormat="1">
+    <row r="40" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:6" s="7" customFormat="1">
+    <row r="41" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42" spans="1:6" s="7" customFormat="1">
+    <row r="42" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" s="7" customFormat="1">
+    <row r="43" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44" spans="1:6" s="7" customFormat="1">
+    <row r="44" spans="1:6" s="7" customFormat="1" ht="15.6">
       <c r="A44" s="8"/>
       <c r="F44" s="8"/>
     </row>
@@ -10326,30 +10364,30 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C1232D-77B5-9843-99FD-ECC7F549C74C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AMJ25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.1640625" defaultRowHeight="22"/>
+  <sheetFormatPr defaultColWidth="7.109375" defaultRowHeight="22.2"/>
   <cols>
     <col min="1" max="1" width="36.6640625" style="57" customWidth="1"/>
-    <col min="2" max="2" width="41.5" style="57" customWidth="1"/>
+    <col min="2" max="2" width="41.44140625" style="57" customWidth="1"/>
     <col min="3" max="3" width="83.33203125" style="57" customWidth="1"/>
-    <col min="4" max="4" width="83.5" style="57" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" style="76" customWidth="1"/>
+    <col min="4" max="4" width="83.44140625" style="57" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" style="76" customWidth="1"/>
     <col min="6" max="6" width="34.33203125" style="76" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" style="57" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="57" customWidth="1"/>
     <col min="8" max="8" width="25" style="76" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" style="76" customWidth="1"/>
-    <col min="10" max="1024" width="7.5" style="57" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" style="76" customWidth="1"/>
+    <col min="10" max="1024" width="7.44140625" style="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024" ht="26">
+    <row r="1" spans="1:1024" ht="24.6">
       <c r="A1" s="54" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
       <c r="D1" s="54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E1" s="55"/>
       <c r="F1" s="55"/>
@@ -10357,7 +10395,7 @@
       <c r="H1" s="56"/>
       <c r="I1" s="56"/>
     </row>
-    <row r="2" spans="1:1024" ht="26">
+    <row r="2" spans="1:1024" ht="24.6">
       <c r="A2" s="55" t="s">
         <v>0</v>
       </c>
@@ -10371,39 +10409,39 @@
         <v>3</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I2" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1024" ht="409.6">
       <c r="A3" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="D3" s="54" t="s">
         <v>113</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>115</v>
       </c>
       <c r="E3" s="55" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>11</v>
@@ -10411,24 +10449,24 @@
       <c r="H3" s="56"/>
       <c r="I3" s="56"/>
     </row>
-    <row r="4" spans="1:1024" ht="383" customHeight="1">
+    <row r="4" spans="1:1024" ht="382.95" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B4" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>117</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>119</v>
       </c>
       <c r="E4" s="55" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>11</v>
@@ -10436,49 +10474,49 @@
       <c r="H4" s="56"/>
       <c r="I4" s="56"/>
     </row>
-    <row r="5" spans="1:1024" ht="283" customHeight="1">
+    <row r="5" spans="1:1024" ht="283.05" customHeight="1">
       <c r="A5" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B5" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="E5" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="F5" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="G5" s="59" t="s">
         <v>123</v>
-      </c>
-      <c r="F5" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="G5" s="59" t="s">
-        <v>125</v>
       </c>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
     </row>
-    <row r="6" spans="1:1024" ht="234">
+    <row r="6" spans="1:1024" ht="221.4">
       <c r="A6" s="55" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>126</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>128</v>
       </c>
       <c r="E6" s="55" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>11</v>
@@ -10488,70 +10526,70 @@
     </row>
     <row r="7" spans="1:1024" ht="354" customHeight="1">
       <c r="A7" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="E7" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="F7" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="I7" s="56"/>
+    </row>
+    <row r="8" spans="1:1024" ht="352.05" customHeight="1">
+      <c r="A8" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="G7" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="61" t="s">
+      <c r="C8" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="I7" s="56"/>
-    </row>
-    <row r="8" spans="1:1024" ht="352" customHeight="1">
-      <c r="A8" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="59" t="s">
+      <c r="D8" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="I8" s="56"/>
+    </row>
+    <row r="9" spans="1:1024" ht="103.05" customHeight="1">
+      <c r="A9" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="B9" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="E8" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="61" t="s">
+      <c r="C9" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="I8" s="56"/>
-    </row>
-    <row r="9" spans="1:1024" ht="103" customHeight="1">
-      <c r="A9" s="55" t="s">
+      <c r="D9" s="54" t="s">
         <v>138</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>140</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="56"/>
@@ -10559,9 +10597,9 @@
       <c r="H9" s="56"/>
       <c r="I9" s="56"/>
     </row>
-    <row r="10" spans="1:1024" ht="28" customHeight="1">
+    <row r="10" spans="1:1024" ht="28.05" customHeight="1">
       <c r="A10" s="143" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" s="144"/>
       <c r="C10" s="144"/>
@@ -10572,24 +10610,24 @@
       <c r="H10" s="145"/>
       <c r="I10" s="146"/>
     </row>
-    <row r="11" spans="1:1024" s="66" customFormat="1" ht="130">
+    <row r="11" spans="1:1024" s="66" customFormat="1" ht="123">
       <c r="A11" s="62" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="63" t="s">
         <v>142</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>144</v>
       </c>
       <c r="E11" s="62" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="62" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G11" s="62" t="s">
         <v>11</v>
@@ -11617,22 +11655,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E12" s="62" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
@@ -12657,19 +12695,19 @@
         <v>25</v>
       </c>
       <c r="B13" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="67" t="s">
         <v>149</v>
-      </c>
-      <c r="C13" s="67" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="67" t="s">
-        <v>151</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>11</v>
@@ -12677,24 +12715,24 @@
       <c r="H13" s="56"/>
       <c r="I13" s="56"/>
     </row>
-    <row r="14" spans="1:1024" ht="208">
+    <row r="14" spans="1:1024" ht="196.8">
       <c r="A14" s="58" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="67" t="s">
         <v>152</v>
-      </c>
-      <c r="C14" s="67" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="67" t="s">
-        <v>154</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>11</v>
@@ -12702,24 +12740,24 @@
       <c r="H14" s="56"/>
       <c r="I14" s="56"/>
     </row>
-    <row r="15" spans="1:1024" ht="286">
+    <row r="15" spans="1:1024" ht="270.60000000000002">
       <c r="A15" s="58" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="67" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D15" s="67" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>11</v>
@@ -12727,101 +12765,101 @@
       <c r="H15" s="56"/>
       <c r="I15" s="56"/>
     </row>
-    <row r="16" spans="1:1024" ht="182">
+    <row r="16" spans="1:1024" ht="172.2">
       <c r="A16" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="D16" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="E16" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="F16" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="G16" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="H16" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="G16" s="68" t="s">
+      <c r="I16" s="70"/>
+    </row>
+    <row r="17" spans="1:9" ht="172.2">
+      <c r="A17" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="H16" s="70" t="s">
+      <c r="C17" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="69" t="s">
         <v>165</v>
       </c>
-      <c r="I16" s="70"/>
-    </row>
-    <row r="17" spans="1:9" ht="182">
-      <c r="A17" s="68" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="68" t="s">
+      <c r="E17" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="69" t="s">
+      <c r="F17" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="E17" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" s="68" t="s">
-        <v>169</v>
-      </c>
       <c r="G17" s="70" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H17" s="70"/>
       <c r="I17" s="70"/>
     </row>
-    <row r="18" spans="1:9" ht="158" customHeight="1">
+    <row r="18" spans="1:9" ht="157.94999999999999" customHeight="1">
       <c r="A18" s="68" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B18" s="68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D18" s="69" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F18" s="68" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G18" s="70" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H18" s="70"/>
       <c r="I18" s="70"/>
     </row>
-    <row r="19" spans="1:9" ht="158" customHeight="1">
+    <row r="19" spans="1:9" ht="157.94999999999999" customHeight="1">
       <c r="A19" s="68" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B19" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="69" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="C19" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>174</v>
-      </c>
       <c r="E19" s="68" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F19" s="68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G19" s="68" t="s">
         <v>11</v>
@@ -12829,7 +12867,7 @@
       <c r="H19" s="70"/>
       <c r="I19" s="70"/>
     </row>
-    <row r="20" spans="1:9" ht="25">
+    <row r="20" spans="1:9" ht="24.6">
       <c r="A20" s="71"/>
       <c r="B20" s="71"/>
       <c r="C20" s="71"/>
@@ -12840,19 +12878,19 @@
       <c r="H20" s="72"/>
       <c r="I20" s="72"/>
     </row>
-    <row r="21" spans="1:9" ht="25">
+    <row r="21" spans="1:9" ht="24.6">
       <c r="A21" s="71"/>
       <c r="B21" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="74" t="s">
+      <c r="E21" s="73" t="s">
         <v>176</v>
-      </c>
-      <c r="D21" s="75" t="s">
-        <v>177</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>178</v>
       </c>
       <c r="F21" s="73" t="s">
         <v>0</v>
@@ -12861,7 +12899,7 @@
       <c r="H21" s="72"/>
       <c r="I21" s="72"/>
     </row>
-    <row r="22" spans="1:9" ht="25">
+    <row r="22" spans="1:9" ht="24.6">
       <c r="A22" s="71"/>
       <c r="B22" s="73" t="s">
         <v>24</v>
@@ -12873,16 +12911,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F22" s="73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G22" s="71"/>
       <c r="H22" s="72"/>
       <c r="I22" s="72"/>
     </row>
-    <row r="23" spans="1:9" ht="25">
+    <row r="23" spans="1:9" ht="24.6">
       <c r="A23" s="71"/>
       <c r="B23" s="73" t="s">
         <v>24</v>
@@ -12894,16 +12932,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F23" s="73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G23" s="71"/>
       <c r="H23" s="72"/>
       <c r="I23" s="72"/>
     </row>
-    <row r="24" spans="1:9" ht="25">
+    <row r="24" spans="1:9" ht="24.6">
       <c r="A24" s="71"/>
       <c r="B24" s="73" t="s">
         <v>24</v>
@@ -12915,16 +12953,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F24" s="73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G24" s="71"/>
       <c r="H24" s="72"/>
       <c r="I24" s="72"/>
     </row>
-    <row r="25" spans="1:9" ht="25">
+    <row r="25" spans="1:9" ht="24.6">
       <c r="A25" s="71"/>
       <c r="B25" s="73" t="s">
         <v>24</v>
@@ -12936,10 +12974,10 @@
         <v>0</v>
       </c>
       <c r="E25" s="73" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F25" s="73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G25" s="71"/>
       <c r="H25" s="72"/>
